--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2022_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2022_maule.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:42</t>
+    <t xml:space="preserve">2026-09-09 20:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2022_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2022_maule.xlsx
@@ -24,87 +24,87 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Talca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constitución</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curepto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empedrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelarco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pencahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Claro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Clemente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rafael</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cauquenes</t>
   </si>
   <si>
     <t xml:space="preserve">Chanco</t>
   </si>
   <si>
+    <t xml:space="preserve">Pelluhue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curicó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualañé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licantén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romeral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sagrada Familia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vichuquén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linares</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colbún</t>
   </si>
   <si>
-    <t xml:space="preserve">Constitución</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curepto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curicó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empedrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualañé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licantén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linares</t>
-  </si>
-  <si>
     <t xml:space="preserve">Longaví</t>
   </si>
   <si>
-    <t xml:space="preserve">Molina</t>
-  </si>
-  <si>
     <t xml:space="preserve">Parral</t>
   </si>
   <si>
-    <t xml:space="preserve">Pelarco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelluhue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pencahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rauco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Retiro</t>
   </si>
   <si>
-    <t xml:space="preserve">Río Claro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romeral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sagrada Familia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Clemente</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Javier</t>
   </si>
   <si>
-    <t xml:space="preserve">San Rafael</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vichuquén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Villa Alegre</t>
   </si>
   <si>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:46</t>
+    <t xml:space="preserve">2026-09-18 10:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -532,7 +532,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.76</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="4">
@@ -548,7 +548,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.06</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.78</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="6">
@@ -564,7 +564,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="7">
@@ -572,7 +572,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="8">
@@ -580,7 +580,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3.01</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +588,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1.82</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="10">
@@ -596,7 +596,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3.19</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="12">
@@ -612,7 +612,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>3.42</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="13">
@@ -620,7 +620,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>3.05</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="14">
@@ -628,7 +628,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3.14</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="15">
@@ -636,7 +636,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2.54</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="16">
@@ -644,7 +644,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1.94</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="17">
@@ -652,7 +652,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2.63</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="18">
@@ -668,7 +668,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>3.24</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="20">
@@ -676,7 +676,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>4.07</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="21">
@@ -684,7 +684,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="22">
@@ -692,7 +692,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1.9</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="23">
@@ -700,7 +700,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2.16</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="24">
@@ -708,7 +708,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="25">
@@ -716,7 +716,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2.25</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="26">
@@ -724,7 +724,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2.51</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="27">
@@ -732,7 +732,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2.56</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="28">
@@ -740,7 +740,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>2.85</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="29">
